--- a/Aug_2026/Daily Sales/25-08-26/Gourmet Food OK.xlsx
+++ b/Aug_2026/Daily Sales/25-08-26/Gourmet Food OK.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322E7F74-3C5C-42D6-AEB3-721F28A3CFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531E0C3E-E137-40F1-B165-5FB45F6758A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -49,6 +49,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2'!$A$1:$P$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -1626,12 +1627,6 @@
     <t>Address: Multan Road</t>
   </si>
   <si>
-    <t xml:space="preserve">Gourmet Food Rizwan Garden </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address: Rizwan Garden </t>
-  </si>
-  <si>
     <t xml:space="preserve">Gourmet Food Yateem Khana </t>
   </si>
   <si>
@@ -1702,6 +1697,12 @@
   </si>
   <si>
     <t xml:space="preserve">Address: Shadra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Rewaz Garden </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address: Rewaz Garden </t>
   </si>
 </sst>
 </file>
@@ -7297,7 +7298,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -7353,7 +7354,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -8721,7 +8722,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -8777,7 +8778,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -10145,7 +10146,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -10201,7 +10202,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -11569,7 +11570,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -11625,7 +11626,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -12993,7 +12994,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -13049,7 +13050,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -14417,7 +14418,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -14473,7 +14474,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -15841,7 +15842,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -15897,7 +15898,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -17273,7 +17274,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -17329,7 +17330,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -18699,7 +18700,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -18755,7 +18756,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -20125,7 +20126,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -20181,7 +20182,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -48029,7 +48030,7 @@
       <c r="L4" s="371"/>
       <c r="M4" s="401">
         <f ca="1">TODAY()+1</f>
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="N4" s="401"/>
       <c r="O4" s="401"/>
@@ -48057,7 +48058,7 @@
       <c r="L5" s="371"/>
       <c r="M5" s="401">
         <f ca="1">M4-1</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="N5" s="370"/>
       <c r="O5" s="370"/>
@@ -54255,7 +54256,7 @@
       <c r="G3" s="361"/>
       <c r="H3" s="358">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="I3" s="358"/>
       <c r="J3" s="359"/>
@@ -54294,7 +54295,7 @@
       </c>
       <c r="S4" s="319" t="str">
         <f>+'2'!A6:A6</f>
-        <v xml:space="preserve">Gourmet Food Rizwan Garden </v>
+        <v xml:space="preserve">Gourmet Food Rewaz Garden </v>
       </c>
       <c r="T4" s="301">
         <f>+'2'!P35</f>
@@ -57233,7 +57234,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -57289,7 +57290,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -58529,7 +58530,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -58657,7 +58658,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -58713,7 +58714,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -61507,7 +61508,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -61563,7 +61564,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
